--- a/optaplanner-examples/data/flightcrewscheduling/unsolved/700flights-28days-Europe.xlsx
+++ b/optaplanner-examples/data/flightcrewscheduling/unsolved/700flights-28days-Europe.xlsx
@@ -10033,7 +10033,7 @@
       <c r="G3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -10054,7 +10054,7 @@
       <c r="N3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -10078,7 +10078,7 @@
       <c r="V3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" s="2" t="s">
         <v>74</v>
       </c>
       <c r="X3" s="3" t="s">
@@ -10125,13 +10125,13 @@
       <c r="F4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="G4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -10149,10 +10149,10 @@
       <c r="N4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="P4" s="3" t="s">
+      <c r="O4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q4" s="2" t="s">
@@ -10164,7 +10164,7 @@
       <c r="S4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="T4" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U4" s="2" t="s">
@@ -10211,7 +10211,7 @@
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -10226,7 +10226,7 @@
       <c r="H5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J5" s="2" t="s">
@@ -10238,7 +10238,7 @@
       <c r="L5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N5" s="2" t="s">
@@ -10268,7 +10268,7 @@
       <c r="V5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="W5" s="3" t="s">
         <v>74</v>
       </c>
       <c r="X5" s="2" t="s">
@@ -10280,7 +10280,7 @@
       <c r="Z5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA5" s="3" t="s">
+      <c r="AA5" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB5" s="2" t="s">
@@ -10292,7 +10292,7 @@
       <c r="AD5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE5" s="3" t="s">
+      <c r="AE5" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -10315,7 +10315,7 @@
       <c r="F6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -10324,10 +10324,10 @@
       <c r="I6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K6" s="3" t="s">
+      <c r="J6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L6" s="2" t="s">
@@ -10407,7 +10407,7 @@
       <c r="E7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
@@ -10437,7 +10437,7 @@
       <c r="O7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P7" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Q7" s="2" t="s">
@@ -10446,10 +10446,10 @@
       <c r="R7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="T7" s="2" t="s">
+      <c r="S7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T7" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U7" s="2" t="s">
@@ -10464,7 +10464,7 @@
       <c r="X7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y7" s="3" t="s">
+      <c r="Y7" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z7" s="2" t="s">
@@ -10473,7 +10473,7 @@
       <c r="AA7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB7" s="3" t="s">
+      <c r="AB7" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC7" s="2" t="s">
@@ -10496,7 +10496,7 @@
       <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -10520,13 +10520,13 @@
       <c r="K8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O8" s="2" t="s">
@@ -10538,7 +10538,7 @@
       <c r="Q8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="R8" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S8" s="2" t="s">
@@ -10571,13 +10571,13 @@
       <c r="AB8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC8" s="3" t="s">
+      <c r="AC8" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE8" s="2" t="s">
+      <c r="AE8" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -10645,7 +10645,7 @@
       <c r="U9" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V9" s="3" t="s">
+      <c r="V9" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W9" s="2" t="s">
@@ -10657,10 +10657,10 @@
       <c r="Y9" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA9" s="2" t="s">
+      <c r="Z9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA9" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AB9" s="2" t="s">
@@ -10784,7 +10784,7 @@
       <c r="D11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -10808,7 +10808,7 @@
       <c r="L11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N11" s="2" t="s">
@@ -10832,7 +10832,7 @@
       <c r="T11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U11" s="3" t="s">
+      <c r="U11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V11" s="2" t="s">
@@ -11087,7 +11087,7 @@
       <c r="J14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="3" t="s">
         <v>74</v>
       </c>
       <c r="L14" s="2" t="s">
@@ -11102,10 +11102,10 @@
       <c r="O14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="P14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q14" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R14" s="2" t="s">
@@ -11123,16 +11123,16 @@
       <c r="V14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="W14" s="2" t="s">
         <v>74</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z14" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA14" s="2" t="s">
@@ -11141,13 +11141,13 @@
       <c r="AB14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AC14" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AE14" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
         <v>116</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>18</v>
@@ -11164,7 +11164,7 @@
       <c r="D15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -11173,7 +11173,7 @@
       <c r="G15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -11182,16 +11182,16 @@
       <c r="J15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N15" s="3" t="s">
+      <c r="M15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O15" s="2" t="s">
@@ -11206,13 +11206,13 @@
       <c r="R15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S15" s="2" t="s">
+      <c r="S15" s="3" t="s">
         <v>74</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U15" s="3" t="s">
+      <c r="U15" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V15" s="2" t="s">
@@ -11251,21 +11251,21 @@
         <v>117</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="F16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -11286,7 +11286,7 @@
       <c r="M16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O16" s="2" t="s">
@@ -11298,7 +11298,7 @@
       <c r="Q16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="R16" s="3" t="s">
         <v>74</v>
       </c>
       <c r="S16" s="2" t="s">
@@ -11375,7 +11375,7 @@
       <c r="K17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="L17" s="3" t="s">
         <v>74</v>
       </c>
       <c r="M17" s="2" t="s">
@@ -11470,7 +11470,7 @@
       <c r="K18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="L18" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M18" s="2" t="s">
@@ -11500,7 +11500,7 @@
       <c r="U18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V18" s="3" t="s">
+      <c r="V18" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W18" s="2" t="s">
@@ -11521,7 +11521,7 @@
       <c r="AB18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC18" s="2" t="s">
+      <c r="AC18" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AD18" s="2" t="s">
@@ -11556,7 +11556,7 @@
       <c r="H19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J19" s="2" t="s">
@@ -11583,10 +11583,10 @@
       <c r="Q19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="S19" s="3" t="s">
+      <c r="R19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="S19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T19" s="2" t="s">
@@ -11595,13 +11595,13 @@
       <c r="U19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V19" s="2" t="s">
+      <c r="V19" s="3" t="s">
         <v>74</v>
       </c>
       <c r="W19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X19" s="3" t="s">
+      <c r="X19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y19" s="2" t="s">
@@ -11639,7 +11639,7 @@
       <c r="D20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -11699,13 +11699,13 @@
       <c r="X20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z20" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA20" s="3" t="s">
+      <c r="Y20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA20" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB20" s="2" t="s">
@@ -11734,10 +11734,10 @@
       <c r="D21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G21" s="2" t="s">
@@ -11752,7 +11752,7 @@
       <c r="J21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L21" s="2" t="s">
@@ -11761,28 +11761,28 @@
       <c r="M21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="P21" s="3" t="s">
+      <c r="N21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R21" s="3" t="s">
+      <c r="R21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="U21" s="2" t="s">
+      <c r="T21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>74</v>
       </c>
       <c r="V21" s="2" t="s">
@@ -11809,7 +11809,7 @@
       <c r="AC21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD21" s="3" t="s">
+      <c r="AD21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE21" s="2" t="s">
@@ -11821,18 +11821,18 @@
         <v>123</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G22" s="2" t="s">
@@ -11844,7 +11844,7 @@
       <c r="I22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K22" s="2" t="s">
@@ -11853,13 +11853,13 @@
       <c r="L22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="M22" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="O22" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P22" s="2" t="s">
@@ -11883,7 +11883,7 @@
       <c r="V22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W22" s="2" t="s">
+      <c r="W22" s="3" t="s">
         <v>74</v>
       </c>
       <c r="X22" s="2" t="s">
@@ -11898,7 +11898,7 @@
       <c r="AA22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB22" s="3" t="s">
+      <c r="AB22" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC22" s="2" t="s">
@@ -11921,22 +11921,22 @@
       <c r="C23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I23" s="2" t="s">
+      <c r="H23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J23" s="2" t="s">
@@ -11972,10 +11972,10 @@
       <c r="T23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="V23" s="3" t="s">
+      <c r="U23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="V23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W23" s="2" t="s">
@@ -11984,7 +11984,7 @@
       <c r="X23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y23" s="2" t="s">
+      <c r="Y23" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Z23" s="2" t="s">
@@ -11999,7 +11999,7 @@
       <c r="AC23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD23" s="3" t="s">
+      <c r="AD23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE23" s="2" t="s">
@@ -12011,7 +12011,7 @@
         <v>125</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>17</v>
@@ -12025,7 +12025,7 @@
       <c r="F24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H24" s="2" t="s">
@@ -12040,7 +12040,7 @@
       <c r="K24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="L24" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M24" s="2" t="s">
@@ -12061,10 +12061,10 @@
       <c r="R24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="T24" s="3" t="s">
+      <c r="S24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="T24" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U24" s="2" t="s">
@@ -12073,19 +12073,19 @@
       <c r="V24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X24" s="2" t="s">
+      <c r="W24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X24" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Y24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA24" s="3" t="s">
+      <c r="Z24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA24" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB24" s="2" t="s">
@@ -12120,13 +12120,13 @@
       <c r="F25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="G25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J25" s="2" t="s">
@@ -12156,7 +12156,7 @@
       <c r="R25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S25" s="3" t="s">
+      <c r="S25" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T25" s="2" t="s">
@@ -12171,10 +12171,10 @@
       <c r="W25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y25" s="3" t="s">
+      <c r="X25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y25" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z25" s="2" t="s">
@@ -12186,13 +12186,13 @@
       <c r="AB25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE25" s="3" t="s">
+      <c r="AC25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE25" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
         <v>127</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>18</v>
@@ -12233,7 +12233,7 @@
       <c r="L26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M26" s="3" t="s">
+      <c r="M26" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N26" s="2" t="s">
@@ -12248,7 +12248,7 @@
       <c r="Q26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R26" s="2" t="s">
+      <c r="R26" s="3" t="s">
         <v>74</v>
       </c>
       <c r="S26" s="2" t="s">
@@ -12266,7 +12266,7 @@
       <c r="W26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X26" s="3" t="s">
+      <c r="X26" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y26" s="2" t="s">
@@ -12278,10 +12278,10 @@
       <c r="AA26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC26" s="3" t="s">
+      <c r="AB26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC26" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD26" s="2" t="s">
@@ -12322,16 +12322,16 @@
       <c r="J27" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L27" s="2" t="s">
+      <c r="K27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>74</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="N27" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O27" s="2" t="s">
@@ -12352,7 +12352,7 @@
       <c r="T27" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U27" s="2" t="s">
+      <c r="U27" s="3" t="s">
         <v>74</v>
       </c>
       <c r="V27" s="2" t="s">
@@ -12367,7 +12367,7 @@
       <c r="Y27" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z27" s="3" t="s">
+      <c r="Z27" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA27" s="2" t="s">
@@ -12391,12 +12391,12 @@
         <v>129</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -12408,7 +12408,7 @@
       <c r="G28" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I28" s="2" t="s">
@@ -12417,7 +12417,7 @@
       <c r="J28" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K28" s="3" t="s">
         <v>74</v>
       </c>
       <c r="L28" s="2" t="s">
@@ -12462,7 +12462,7 @@
       <c r="Y28" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z28" s="2" t="s">
+      <c r="Z28" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AA28" s="2" t="s">
@@ -12509,7 +12509,7 @@
       <c r="I29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K29" s="2" t="s">
@@ -12524,7 +12524,7 @@
       <c r="N29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O29" s="2" t="s">
+      <c r="O29" s="3" t="s">
         <v>74</v>
       </c>
       <c r="P29" s="2" t="s">
@@ -12533,7 +12533,7 @@
       <c r="Q29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R29" s="3" t="s">
+      <c r="R29" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S29" s="2" t="s">
@@ -12613,7 +12613,7 @@
       <c r="L30" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="M30" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N30" s="2" t="s">
@@ -12661,7 +12661,7 @@
       <c r="AB30" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC30" s="2" t="s">
+      <c r="AC30" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AD30" s="2" t="s">
@@ -12699,7 +12699,7 @@
       <c r="I31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="3" t="s">
         <v>74</v>
       </c>
       <c r="K31" s="2" t="s">
@@ -12711,7 +12711,7 @@
       <c r="M31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="N31" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O31" s="2" t="s">
@@ -12720,7 +12720,7 @@
       <c r="P31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q31" s="3" t="s">
+      <c r="Q31" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R31" s="2" t="s">
@@ -12744,7 +12744,7 @@
       <c r="X31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y31" s="3" t="s">
+      <c r="Y31" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z31" s="2" t="s">
@@ -12759,10 +12759,10 @@
       <c r="AC31" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD31" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE31" s="3" t="s">
+      <c r="AD31" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE31" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -12824,13 +12824,13 @@
       <c r="S32" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T32" s="2" t="s">
+      <c r="T32" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U32" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V32" s="2" t="s">
+      <c r="V32" s="3" t="s">
         <v>74</v>
       </c>
       <c r="W32" s="2" t="s">
@@ -12866,7 +12866,7 @@
         <v>134</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>17</v>
@@ -12880,7 +12880,7 @@
       <c r="F33" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H33" s="2" t="s">
@@ -12922,7 +12922,7 @@
       <c r="T33" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U33" s="3" t="s">
+      <c r="U33" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V33" s="2" t="s">
@@ -13035,10 +13035,10 @@
       <c r="Z34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA34" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB34" s="2" t="s">
+      <c r="AA34" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB34" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AC34" s="2" t="s">
@@ -13047,7 +13047,7 @@
       <c r="AD34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE34" s="2" t="s">
+      <c r="AE34" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -13056,7 +13056,7 @@
         <v>136</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>18</v>
@@ -13067,7 +13067,7 @@
       <c r="E35" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G35" s="2" t="s">
@@ -13085,7 +13085,7 @@
       <c r="K35" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L35" s="3" t="s">
+      <c r="L35" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M35" s="2" t="s">
@@ -13106,16 +13106,16 @@
       <c r="R35" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="T35" s="3" t="s">
+      <c r="S35" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T35" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V35" s="2" t="s">
+      <c r="V35" s="3" t="s">
         <v>74</v>
       </c>
       <c r="W35" s="2" t="s">
@@ -13228,7 +13228,7 @@
       <c r="AA36" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB36" s="2" t="s">
+      <c r="AB36" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AC36" s="2" t="s">
@@ -13246,7 +13246,7 @@
         <v>138</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>18</v>
@@ -13254,7 +13254,7 @@
       <c r="D37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F37" s="2" t="s">
@@ -13266,7 +13266,7 @@
       <c r="H37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J37" s="2" t="s">
@@ -13278,7 +13278,7 @@
       <c r="L37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="M37" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N37" s="2" t="s">
@@ -13305,7 +13305,7 @@
       <c r="U37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V37" s="3" t="s">
+      <c r="V37" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W37" s="2" t="s">
@@ -13320,7 +13320,7 @@
       <c r="Z37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA37" s="3" t="s">
+      <c r="AA37" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB37" s="2" t="s">
@@ -13376,7 +13376,7 @@
       <c r="M38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="N38" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O38" s="3" t="s">
@@ -13388,7 +13388,7 @@
       <c r="Q38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R38" s="2" t="s">
+      <c r="R38" s="3" t="s">
         <v>74</v>
       </c>
       <c r="S38" s="2" t="s">
@@ -13441,13 +13441,13 @@
       <c r="C39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F39" s="3" t="s">
+      <c r="D39" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G39" s="2" t="s">
@@ -13465,7 +13465,7 @@
       <c r="K39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="L39" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M39" s="2" t="s">
@@ -13495,7 +13495,7 @@
       <c r="U39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V39" s="3" t="s">
+      <c r="V39" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W39" s="2" t="s">
@@ -13531,7 +13531,7 @@
         <v>141</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>18</v>
@@ -13578,7 +13578,7 @@
       <c r="Q40" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R40" s="3" t="s">
+      <c r="R40" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S40" s="2" t="s">
@@ -13602,7 +13602,7 @@
       <c r="Y40" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z40" s="2" t="s">
+      <c r="Z40" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AA40" s="2" t="s">
@@ -13614,7 +13614,7 @@
       <c r="AC40" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD40" s="3" t="s">
+      <c r="AD40" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE40" s="2" t="s">
@@ -13643,7 +13643,7 @@
       <c r="G41" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I41" s="2" t="s">
@@ -13661,7 +13661,7 @@
       <c r="M41" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N41" s="3" t="s">
+      <c r="N41" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O41" s="2" t="s">
@@ -13679,7 +13679,7 @@
       <c r="S41" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T41" s="3" t="s">
+      <c r="T41" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U41" s="2" t="s">
@@ -13694,7 +13694,7 @@
       <c r="X41" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y41" s="3" t="s">
+      <c r="Y41" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z41" s="2" t="s">
@@ -13721,7 +13721,7 @@
         <v>143</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>18</v>
@@ -13741,7 +13741,7 @@
       <c r="H42" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J42" s="2" t="s">
@@ -13771,7 +13771,7 @@
       <c r="R42" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S42" s="2" t="s">
+      <c r="S42" s="3" t="s">
         <v>74</v>
       </c>
       <c r="T42" s="2" t="s">
@@ -13795,13 +13795,13 @@
       <c r="Z42" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA42" s="2" t="s">
+      <c r="AA42" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AB42" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC42" s="2" t="s">
+      <c r="AC42" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AD42" s="2" t="s">
@@ -13842,7 +13842,7 @@
       <c r="J43" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K43" s="3" t="s">
+      <c r="K43" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L43" s="2" t="s">
@@ -13860,7 +13860,7 @@
       <c r="P43" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q43" s="2" t="s">
+      <c r="Q43" s="3" t="s">
         <v>74</v>
       </c>
       <c r="R43" s="2" t="s">
@@ -13872,7 +13872,7 @@
       <c r="T43" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U43" s="3" t="s">
+      <c r="U43" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V43" s="2" t="s">
@@ -13890,10 +13890,10 @@
       <c r="Z43" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB43" s="3" t="s">
+      <c r="AA43" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB43" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC43" s="2" t="s">
@@ -13928,13 +13928,13 @@
       <c r="G44" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H44" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K44" s="2" t="s">
@@ -13961,7 +13961,7 @@
       <c r="R44" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S44" s="3" t="s">
+      <c r="S44" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T44" s="2" t="s">
@@ -14032,25 +14032,25 @@
       <c r="J45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="K45" s="3" t="s">
         <v>74</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="M45" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q45" s="3" t="s">
+      <c r="O45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q45" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R45" s="2" t="s">
@@ -14068,16 +14068,16 @@
       <c r="V45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X45" s="3" t="s">
+      <c r="W45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X45" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z45" s="3" t="s">
+      <c r="Z45" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA45" s="2" t="s">
@@ -14086,7 +14086,7 @@
       <c r="AB45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC45" s="3" t="s">
+      <c r="AC45" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD45" s="2" t="s">
@@ -14101,7 +14101,7 @@
         <v>147</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>18</v>
@@ -14139,10 +14139,10 @@
       <c r="N46" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="P46" s="3" t="s">
+      <c r="O46" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P46" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q46" s="2" t="s">
@@ -14157,7 +14157,7 @@
       <c r="T46" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U46" s="3" t="s">
+      <c r="U46" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V46" s="2" t="s">
@@ -14169,7 +14169,7 @@
       <c r="X46" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y46" s="3" t="s">
+      <c r="Y46" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z46" s="2" t="s">
@@ -14184,7 +14184,7 @@
       <c r="AC46" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD46" s="3" t="s">
+      <c r="AD46" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE46" s="2" t="s">
@@ -14196,7 +14196,7 @@
         <v>148</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>18</v>
@@ -14210,7 +14210,7 @@
       <c r="F47" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H47" s="2" t="s">
@@ -14243,7 +14243,7 @@
       <c r="Q47" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R47" s="3" t="s">
+      <c r="R47" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S47" s="2" t="s">
@@ -14291,7 +14291,7 @@
         <v>149</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
@@ -14299,7 +14299,7 @@
       <c r="D48" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F48" s="2" t="s">
@@ -14320,13 +14320,13 @@
       <c r="K48" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N48" s="3" t="s">
+      <c r="L48" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N48" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O48" s="2" t="s">
@@ -14347,7 +14347,7 @@
       <c r="T48" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U48" s="2" t="s">
+      <c r="U48" s="3" t="s">
         <v>74</v>
       </c>
       <c r="V48" s="2" t="s">
@@ -14356,22 +14356,22 @@
       <c r="W48" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X48" s="3" t="s">
+      <c r="X48" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y48" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z48" s="3" t="s">
+      <c r="Z48" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA48" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC48" s="3" t="s">
+      <c r="AB48" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC48" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD48" s="2" t="s">
@@ -14386,7 +14386,7 @@
         <v>150</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>17</v>
@@ -14397,7 +14397,7 @@
       <c r="E49" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G49" s="2" t="s">
@@ -14412,7 +14412,7 @@
       <c r="J49" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="K49" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L49" s="2" t="s">
@@ -14427,7 +14427,7 @@
       <c r="O49" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P49" s="2" t="s">
+      <c r="P49" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Q49" s="2" t="s">
@@ -14436,10 +14436,10 @@
       <c r="R49" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="T49" s="3" t="s">
+      <c r="S49" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T49" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U49" s="2" t="s">
@@ -14481,7 +14481,7 @@
         <v>151</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>18</v>
@@ -14489,7 +14489,7 @@
       <c r="D50" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F50" s="2" t="s">
@@ -14501,7 +14501,7 @@
       <c r="H50" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I50" s="2" t="s">
+      <c r="I50" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J50" s="2" t="s">
@@ -14576,7 +14576,7 @@
         <v>152</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>18</v>
@@ -14599,13 +14599,13 @@
       <c r="I51" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="J51" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L51" s="2" t="s">
+      <c r="L51" s="3" t="s">
         <v>74</v>
       </c>
       <c r="M51" s="2" t="s">
@@ -14629,7 +14629,7 @@
       <c r="S51" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T51" s="2" t="s">
+      <c r="T51" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U51" s="2" t="s">
@@ -14662,7 +14662,7 @@
       <c r="AD51" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE51" s="3" t="s">
+      <c r="AE51" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
       <c r="P52" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q52" s="3" t="s">
+      <c r="Q52" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R52" s="2" t="s">
@@ -14745,7 +14745,7 @@
       <c r="Z52" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA52" s="3" t="s">
+      <c r="AA52" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB52" s="2" t="s">
@@ -14754,7 +14754,7 @@
       <c r="AC52" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD52" s="2" t="s">
+      <c r="AD52" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AE52" s="2" t="s">
@@ -14766,7 +14766,7 @@
         <v>154</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
@@ -14777,16 +14777,16 @@
       <c r="E53" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H53" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I53" s="3" t="s">
+      <c r="H53" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I53" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J53" s="2" t="s">
@@ -14825,10 +14825,10 @@
       <c r="U53" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V53" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="W53" s="3" t="s">
+      <c r="V53" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="W53" s="2" t="s">
         <v>74</v>
       </c>
       <c r="X53" s="2" t="s">
@@ -14861,7 +14861,7 @@
         <v>155</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
@@ -14878,13 +14878,13 @@
       <c r="G54" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J54" s="2" t="s">
+      <c r="H54" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J54" s="3" t="s">
         <v>74</v>
       </c>
       <c r="K54" s="2" t="s">
@@ -14896,7 +14896,7 @@
       <c r="M54" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N54" s="3" t="s">
+      <c r="N54" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O54" s="2" t="s">
@@ -14926,13 +14926,13 @@
       <c r="W54" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X54" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y54" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z54" s="3" t="s">
+      <c r="X54" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z54" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA54" s="2" t="s">
@@ -14956,7 +14956,7 @@
         <v>156</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>18</v>
@@ -15009,7 +15009,7 @@
       <c r="S55" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T55" s="2" t="s">
+      <c r="T55" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U55" s="2" t="s">
@@ -15080,7 +15080,7 @@
       <c r="K56" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L56" s="3" t="s">
+      <c r="L56" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M56" s="2" t="s">
@@ -15089,7 +15089,7 @@
       <c r="N56" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O56" s="3" t="s">
+      <c r="O56" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P56" s="2" t="s">
@@ -15113,7 +15113,7 @@
       <c r="V56" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="W56" s="3" t="s">
+      <c r="W56" s="2" t="s">
         <v>74</v>
       </c>
       <c r="X56" s="2" t="s">
@@ -15146,7 +15146,7 @@
         <v>158</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>18</v>
@@ -15178,7 +15178,7 @@
       <c r="L57" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="M57" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N57" s="2" t="s">
@@ -15226,7 +15226,7 @@
       <c r="AB57" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC57" s="2" t="s">
+      <c r="AC57" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AD57" s="2" t="s">
@@ -15241,7 +15241,7 @@
         <v>159</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>17</v>
@@ -15249,13 +15249,13 @@
       <c r="D58" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G58" s="3" t="s">
+      <c r="E58" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H58" s="2" t="s">
@@ -15324,10 +15324,10 @@
       <c r="AC58" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE58" s="3" t="s">
+      <c r="AD58" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE58" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
         <v>160</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>17</v>
@@ -15362,7 +15362,7 @@
       <c r="J59" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="K59" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L59" s="2" t="s">
@@ -15374,7 +15374,7 @@
       <c r="N59" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O59" s="2" t="s">
+      <c r="O59" s="3" t="s">
         <v>74</v>
       </c>
       <c r="P59" s="2" t="s">
@@ -15389,7 +15389,7 @@
       <c r="S59" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T59" s="3" t="s">
+      <c r="T59" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U59" s="2" t="s">
@@ -15404,7 +15404,7 @@
       <c r="X59" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y59" s="3" t="s">
+      <c r="Y59" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z59" s="2" t="s">
@@ -15413,7 +15413,7 @@
       <c r="AA59" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB59" s="3" t="s">
+      <c r="AB59" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC59" s="2" t="s">
@@ -15431,7 +15431,7 @@
         <v>161</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>18</v>
@@ -15439,7 +15439,7 @@
       <c r="D60" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F60" s="2" t="s">
@@ -15463,7 +15463,7 @@
       <c r="L60" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M60" s="3" t="s">
+      <c r="M60" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N60" s="2" t="s">
@@ -15478,7 +15478,7 @@
       <c r="Q60" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R60" s="3" t="s">
+      <c r="R60" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S60" s="2" t="s">
@@ -15487,7 +15487,7 @@
       <c r="T60" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U60" s="3" t="s">
+      <c r="U60" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V60" s="2" t="s">
@@ -15502,10 +15502,10 @@
       <c r="Y60" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z60" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA60" s="3" t="s">
+      <c r="Z60" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA60" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB60" s="2" t="s">
@@ -15531,7 +15531,7 @@
       <c r="C61" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E61" s="2" t="s">
@@ -15561,13 +15561,13 @@
       <c r="M61" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N61" s="2" t="s">
+      <c r="N61" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P61" s="3" t="s">
+      <c r="P61" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q61" s="2" t="s">
@@ -15591,7 +15591,7 @@
       <c r="W61" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X61" s="3" t="s">
+      <c r="X61" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y61" s="2" t="s">
@@ -15606,7 +15606,7 @@
       <c r="AB61" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC61" s="3" t="s">
+      <c r="AC61" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD61" s="2" t="s">
@@ -15638,7 +15638,7 @@
       <c r="G62" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="H62" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I62" s="2" t="s">
@@ -15650,7 +15650,7 @@
       <c r="K62" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L62" s="2" t="s">
+      <c r="L62" s="3" t="s">
         <v>74</v>
       </c>
       <c r="M62" s="2" t="s">
@@ -15662,7 +15662,7 @@
       <c r="O62" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P62" s="3" t="s">
+      <c r="P62" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q62" s="3" t="s">
@@ -15671,7 +15671,7 @@
       <c r="R62" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S62" s="3" t="s">
+      <c r="S62" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T62" s="2" t="s">
@@ -15721,10 +15721,10 @@
       <c r="C63" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E63" s="3" t="s">
+      <c r="D63" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F63" s="2" t="s">
@@ -15748,7 +15748,7 @@
       <c r="L63" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M63" s="3" t="s">
+      <c r="M63" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N63" s="2" t="s">
@@ -15760,7 +15760,7 @@
       <c r="P63" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q63" s="3" t="s">
+      <c r="Q63" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R63" s="2" t="s">
@@ -15790,7 +15790,7 @@
       <c r="Z63" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA63" s="2" t="s">
+      <c r="AA63" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AB63" s="2" t="s">
@@ -15811,7 +15811,7 @@
         <v>165</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>17</v>
@@ -15906,7 +15906,7 @@
         <v>166</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>18</v>
@@ -15923,16 +15923,16 @@
       <c r="G65" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I65" s="2" t="s">
+      <c r="H65" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K65" s="2" t="s">
+      <c r="K65" s="3" t="s">
         <v>74</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -15959,7 +15959,7 @@
       <c r="S65" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T65" s="3" t="s">
+      <c r="T65" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U65" s="2" t="s">
@@ -15968,13 +15968,13 @@
       <c r="V65" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W65" s="3" t="s">
+      <c r="W65" s="2" t="s">
         <v>74</v>
       </c>
       <c r="X65" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y65" s="2" t="s">
+      <c r="Y65" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Z65" s="2" t="s">
@@ -15983,7 +15983,7 @@
       <c r="AA65" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB65" s="3" t="s">
+      <c r="AB65" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC65" s="2" t="s">
@@ -16012,7 +16012,7 @@
       <c r="E66" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G66" s="2" t="s">
@@ -16027,7 +16027,7 @@
       <c r="J66" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="K66" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L66" s="2" t="s">
@@ -16060,7 +16060,7 @@
       <c r="U66" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V66" s="3" t="s">
+      <c r="V66" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W66" s="2" t="s">
@@ -16075,7 +16075,7 @@
       <c r="Z66" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA66" s="3" t="s">
+      <c r="AA66" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB66" s="2" t="s">
@@ -16087,7 +16087,7 @@
       <c r="AD66" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE66" s="2" t="s">
+      <c r="AE66" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16096,7 +16096,7 @@
         <v>168</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>18</v>
@@ -16116,7 +16116,7 @@
       <c r="H67" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I67" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J67" s="2" t="s">
@@ -16134,10 +16134,10 @@
       <c r="N67" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O67" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="P67" s="2" t="s">
+      <c r="O67" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P67" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Q67" s="2" t="s">
@@ -16164,7 +16164,7 @@
       <c r="X67" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y67" s="3" t="s">
+      <c r="Y67" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z67" s="2" t="s">
@@ -16176,13 +16176,13 @@
       <c r="AB67" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC67" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD67" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE67" s="3" t="s">
+      <c r="AC67" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD67" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE67" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16191,7 +16191,7 @@
         <v>169</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>17</v>
@@ -16256,7 +16256,7 @@
       <c r="W68" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X68" s="2" t="s">
+      <c r="X68" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Y68" s="2" t="s">
@@ -16268,7 +16268,7 @@
       <c r="AA68" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB68" s="2" t="s">
+      <c r="AB68" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AC68" s="2" t="s">
@@ -16286,7 +16286,7 @@
         <v>170</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>17</v>
@@ -16297,7 +16297,7 @@
       <c r="E69" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="F69" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G69" s="2" t="s">
@@ -16321,7 +16321,7 @@
       <c r="M69" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N69" s="3" t="s">
+      <c r="N69" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O69" s="2" t="s">
@@ -16336,7 +16336,7 @@
       <c r="R69" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="S69" s="2" t="s">
+      <c r="S69" s="3" t="s">
         <v>74</v>
       </c>
       <c r="T69" s="2" t="s">
@@ -16348,7 +16348,7 @@
       <c r="V69" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W69" s="2" t="s">
+      <c r="W69" s="3" t="s">
         <v>74</v>
       </c>
       <c r="X69" s="2" t="s">
@@ -16369,7 +16369,7 @@
       <c r="AC69" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD69" s="2" t="s">
+      <c r="AD69" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AE69" s="2" t="s">
@@ -16404,13 +16404,13 @@
       <c r="I70" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="J70" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L70" s="3" t="s">
+      <c r="L70" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M70" s="2" t="s">
@@ -16431,7 +16431,7 @@
       <c r="R70" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S70" s="3" t="s">
+      <c r="S70" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T70" s="2" t="s">
@@ -16446,13 +16446,13 @@
       <c r="W70" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X70" s="3" t="s">
+      <c r="X70" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y70" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z70" s="3" t="s">
+      <c r="Z70" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA70" s="2" t="s">
@@ -16481,10 +16481,10 @@
       <c r="C71" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E71" s="3" t="s">
+      <c r="D71" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F71" s="2" t="s">
@@ -16505,7 +16505,7 @@
       <c r="K71" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L71" s="3" t="s">
+      <c r="L71" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M71" s="2" t="s">
@@ -16571,7 +16571,7 @@
         <v>173</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>18</v>
@@ -16582,13 +16582,13 @@
       <c r="E72" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="F72" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H72" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I72" s="2" t="s">
@@ -16606,7 +16606,7 @@
       <c r="M72" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N72" s="2" t="s">
+      <c r="N72" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O72" s="2" t="s">
@@ -16615,7 +16615,7 @@
       <c r="P72" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q72" s="3" t="s">
+      <c r="Q72" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R72" s="2" t="s">
@@ -16636,13 +16636,13 @@
       <c r="W72" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X72" s="2" t="s">
+      <c r="X72" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Y72" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z72" s="3" t="s">
+      <c r="Z72" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA72" s="2" t="s">
@@ -16651,7 +16651,7 @@
       <c r="AB72" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC72" s="3" t="s">
+      <c r="AC72" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD72" s="2" t="s">
@@ -16671,13 +16671,13 @@
       <c r="C73" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G73" s="2" t="s">
@@ -16686,13 +16686,13 @@
       <c r="H73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I73" s="3" t="s">
+      <c r="I73" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K73" s="3" t="s">
+      <c r="K73" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L73" s="2" t="s">
@@ -16704,7 +16704,7 @@
       <c r="N73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O73" s="3" t="s">
+      <c r="O73" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P73" s="2" t="s">
@@ -16713,7 +16713,7 @@
       <c r="Q73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R73" s="3" t="s">
+      <c r="R73" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S73" s="2" t="s">
@@ -16731,16 +16731,16 @@
       <c r="W73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X73" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y73" s="2" t="s">
+      <c r="X73" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y73" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Z73" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA73" s="3" t="s">
+      <c r="AA73" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB73" s="2" t="s">
@@ -16761,7 +16761,7 @@
         <v>175</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>17</v>
@@ -16793,10 +16793,10 @@
       <c r="L74" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M74" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N74" s="3" t="s">
+      <c r="M74" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N74" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O74" s="2" t="s">
@@ -16805,7 +16805,7 @@
       <c r="P74" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q74" s="2" t="s">
+      <c r="Q74" s="3" t="s">
         <v>74</v>
       </c>
       <c r="R74" s="2" t="s">
@@ -16817,13 +16817,13 @@
       <c r="T74" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="U74" s="3" t="s">
+      <c r="U74" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V74" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W74" s="3" t="s">
+      <c r="W74" s="2" t="s">
         <v>74</v>
       </c>
       <c r="X74" s="2" t="s">
@@ -16847,7 +16847,7 @@
       <c r="AD74" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE74" s="3" t="s">
+      <c r="AE74" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
         <v>176</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>18</v>
@@ -16870,7 +16870,7 @@
       <c r="F75" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H75" s="2" t="s">
@@ -16894,10 +16894,10 @@
       <c r="N75" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O75" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="P75" s="2" t="s">
+      <c r="O75" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P75" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Q75" s="2" t="s">
@@ -16912,7 +16912,7 @@
       <c r="T75" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U75" s="2" t="s">
+      <c r="U75" s="3" t="s">
         <v>74</v>
       </c>
       <c r="V75" s="2" t="s">
@@ -16924,7 +16924,7 @@
       <c r="X75" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y75" s="3" t="s">
+      <c r="Y75" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z75" s="2" t="s">
@@ -16936,7 +16936,7 @@
       <c r="AB75" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC75" s="2" t="s">
+      <c r="AC75" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AD75" s="2" t="s">
@@ -16959,7 +16959,7 @@
       <c r="D76" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E76" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F76" s="2" t="s">
@@ -16980,10 +16980,10 @@
       <c r="K76" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L76" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M76" s="2" t="s">
+      <c r="L76" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M76" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N76" s="2" t="s">
@@ -17028,13 +17028,13 @@
       <c r="AA76" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB76" s="3" t="s">
+      <c r="AB76" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC76" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD76" s="3" t="s">
+      <c r="AD76" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE76" s="2" t="s">
@@ -17046,7 +17046,7 @@
         <v>178</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>18</v>
@@ -17060,7 +17060,7 @@
       <c r="F77" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H77" s="2" t="s">
@@ -17087,7 +17087,7 @@
       <c r="O77" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P77" s="3" t="s">
+      <c r="P77" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q77" s="2" t="s">
@@ -17102,10 +17102,10 @@
       <c r="T77" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U77" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="V77" s="3" t="s">
+      <c r="U77" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="V77" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W77" s="2" t="s">
@@ -17114,7 +17114,7 @@
       <c r="X77" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y77" s="3" t="s">
+      <c r="Y77" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z77" s="2" t="s">
@@ -17146,7 +17146,7 @@
       <c r="C78" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -17191,10 +17191,10 @@
       <c r="R78" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S78" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="T78" s="3" t="s">
+      <c r="S78" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="T78" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U78" s="2" t="s">
@@ -17236,7 +17236,7 @@
         <v>180</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
@@ -17244,7 +17244,7 @@
       <c r="D79" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F79" s="2" t="s">
@@ -17265,7 +17265,7 @@
       <c r="K79" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L79" s="3" t="s">
+      <c r="L79" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M79" s="2" t="s">
@@ -17295,10 +17295,10 @@
       <c r="U79" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V79" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="W79" s="2" t="s">
+      <c r="V79" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="W79" s="3" t="s">
         <v>74</v>
       </c>
       <c r="X79" s="2" t="s">
@@ -17313,7 +17313,7 @@
       <c r="AA79" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB79" s="3" t="s">
+      <c r="AB79" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC79" s="2" t="s">
@@ -17331,7 +17331,7 @@
         <v>181</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>18</v>
@@ -17354,7 +17354,7 @@
       <c r="I80" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J80" s="3" t="s">
+      <c r="J80" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K80" s="2" t="s">
@@ -17375,10 +17375,10 @@
       <c r="P80" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q80" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="R80" s="2" t="s">
+      <c r="Q80" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R80" s="3" t="s">
         <v>74</v>
       </c>
       <c r="S80" s="2" t="s">
@@ -17393,7 +17393,7 @@
       <c r="V80" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W80" s="3" t="s">
+      <c r="W80" s="2" t="s">
         <v>74</v>
       </c>
       <c r="X80" s="2" t="s">
@@ -17408,13 +17408,13 @@
       <c r="AA80" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC80" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD80" s="2" t="s">
+      <c r="AB80" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC80" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD80" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AE80" s="2" t="s">
@@ -17426,12 +17426,12 @@
         <v>182</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D81" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -17449,7 +17449,7 @@
       <c r="I81" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J81" s="2" t="s">
+      <c r="J81" s="3" t="s">
         <v>74</v>
       </c>
       <c r="K81" s="2" t="s">
@@ -17497,10 +17497,10 @@
       <c r="Y81" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z81" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA81" s="2" t="s">
+      <c r="Z81" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA81" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AB81" s="2" t="s">
@@ -17535,10 +17535,10 @@
       <c r="F82" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G82" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H82" s="3" t="s">
+      <c r="G82" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I82" s="3" t="s">
@@ -17547,7 +17547,7 @@
       <c r="J82" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K82" s="3" t="s">
+      <c r="K82" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L82" s="2" t="s">
@@ -17559,7 +17559,7 @@
       <c r="N82" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O82" s="3" t="s">
+      <c r="O82" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P82" s="2" t="s">
@@ -17633,7 +17633,7 @@
       <c r="G83" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H83" s="2" t="s">
+      <c r="H83" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I83" s="2" t="s">
@@ -17648,7 +17648,7 @@
       <c r="L83" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="M83" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N83" s="2" t="s">
@@ -17666,7 +17666,7 @@
       <c r="R83" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S83" s="3" t="s">
+      <c r="S83" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T83" s="2" t="s">
@@ -17675,7 +17675,7 @@
       <c r="U83" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V83" s="2" t="s">
+      <c r="V83" s="3" t="s">
         <v>74</v>
       </c>
       <c r="W83" s="2" t="s">
@@ -17711,7 +17711,7 @@
         <v>185</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>17</v>
@@ -17722,7 +17722,7 @@
       <c r="E84" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G84" s="2" t="s">
@@ -17737,7 +17737,7 @@
       <c r="J84" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K84" s="2" t="s">
+      <c r="K84" s="3" t="s">
         <v>74</v>
       </c>
       <c r="L84" s="2" t="s">
@@ -17746,13 +17746,13 @@
       <c r="M84" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N84" s="3" t="s">
+      <c r="N84" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P84" s="3" t="s">
+      <c r="P84" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q84" s="2" t="s">
@@ -17776,7 +17776,7 @@
       <c r="W84" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X84" s="3" t="s">
+      <c r="X84" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y84" s="2" t="s">
@@ -17785,7 +17785,7 @@
       <c r="Z84" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA84" s="3" t="s">
+      <c r="AA84" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB84" s="2" t="s">
@@ -17794,7 +17794,7 @@
       <c r="AC84" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD84" s="3" t="s">
+      <c r="AD84" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE84" s="2" t="s">
@@ -17806,7 +17806,7 @@
         <v>186</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>18</v>
@@ -17823,7 +17823,7 @@
       <c r="G85" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="H85" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I85" s="2" t="s">
@@ -17853,19 +17853,19 @@
       <c r="Q85" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R85" s="3" t="s">
+      <c r="R85" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S85" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T85" s="2" t="s">
+      <c r="T85" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U85" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V85" s="2" t="s">
+      <c r="V85" s="3" t="s">
         <v>74</v>
       </c>
       <c r="W85" s="2" t="s">
@@ -17877,7 +17877,7 @@
       <c r="Y85" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z85" s="3" t="s">
+      <c r="Z85" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA85" s="2" t="s">
@@ -17889,7 +17889,7 @@
       <c r="AC85" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD85" s="3" t="s">
+      <c r="AD85" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE85" s="2" t="s">
@@ -17912,7 +17912,7 @@
       <c r="E86" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G86" s="2" t="s">
@@ -17933,13 +17933,13 @@
       <c r="L86" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M86" s="3" t="s">
+      <c r="M86" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O86" s="3" t="s">
+      <c r="O86" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P86" s="2" t="s">
@@ -17960,10 +17960,10 @@
       <c r="U86" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V86" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="W86" s="2" t="s">
+      <c r="V86" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="W86" s="3" t="s">
         <v>74</v>
       </c>
       <c r="X86" s="2" t="s">
@@ -17978,7 +17978,7 @@
       <c r="AA86" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB86" s="2" t="s">
+      <c r="AB86" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AC86" s="2" t="s">
@@ -17996,7 +17996,7 @@
         <v>188</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>18</v>
@@ -18013,7 +18013,7 @@
       <c r="G87" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H87" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I87" s="2" t="s">
@@ -18061,7 +18061,7 @@
       <c r="W87" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X87" s="2" t="s">
+      <c r="X87" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Y87" s="2" t="s">
@@ -18070,7 +18070,7 @@
       <c r="Z87" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA87" s="2" t="s">
+      <c r="AA87" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AB87" s="2" t="s">
@@ -18105,7 +18105,7 @@
       <c r="F88" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G88" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H88" s="2" t="s">
@@ -18114,19 +18114,19 @@
       <c r="I88" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J88" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L88" s="2" t="s">
+      <c r="J88" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L88" s="3" t="s">
         <v>74</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N88" s="2" t="s">
+      <c r="N88" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O88" s="2" t="s">
@@ -18138,7 +18138,7 @@
       <c r="Q88" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R88" s="3" t="s">
+      <c r="R88" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S88" s="2" t="s">
@@ -18159,7 +18159,7 @@
       <c r="X88" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y88" s="3" t="s">
+      <c r="Y88" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z88" s="2" t="s">
@@ -18186,7 +18186,7 @@
         <v>190</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>17</v>
@@ -18194,7 +18194,7 @@
       <c r="D89" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="E89" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F89" s="2" t="s">
@@ -18242,7 +18242,7 @@
       <c r="T89" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U89" s="2" t="s">
+      <c r="U89" s="3" t="s">
         <v>74</v>
       </c>
       <c r="V89" s="2" t="s">
@@ -18289,7 +18289,7 @@
       <c r="D90" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F90" s="2" t="s">
@@ -18301,7 +18301,7 @@
       <c r="H90" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="I90" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J90" s="2" t="s">
@@ -18313,13 +18313,13 @@
       <c r="L90" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M90" s="2" t="s">
+      <c r="M90" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O90" s="2" t="s">
+      <c r="O90" s="3" t="s">
         <v>74</v>
       </c>
       <c r="P90" s="2" t="s">
@@ -18355,16 +18355,16 @@
       <c r="Z90" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA90" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB90" s="3" t="s">
+      <c r="AA90" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB90" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC90" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD90" s="2" t="s">
+      <c r="AD90" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AE90" s="2" t="s">
@@ -18376,7 +18376,7 @@
         <v>192</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>18</v>
@@ -18390,13 +18390,13 @@
       <c r="F91" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="G91" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I91" s="2" t="s">
+      <c r="I91" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J91" s="2" t="s">
@@ -18420,7 +18420,7 @@
       <c r="P91" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q91" s="3" t="s">
+      <c r="Q91" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R91" s="2" t="s">
@@ -18471,7 +18471,7 @@
         <v>193</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>18</v>
@@ -18497,10 +18497,10 @@
       <c r="J92" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K92" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L92" s="3" t="s">
+      <c r="K92" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L92" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M92" s="2" t="s">
@@ -18521,25 +18521,25 @@
       <c r="R92" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S92" s="3" t="s">
+      <c r="S92" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T92" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U92" s="3" t="s">
+      <c r="U92" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W92" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X92" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y92" s="2" t="s">
+      <c r="W92" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X92" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y92" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Z92" s="2" t="s">
@@ -18551,7 +18551,7 @@
       <c r="AB92" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC92" s="2" t="s">
+      <c r="AC92" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AD92" s="2" t="s">
@@ -18566,12 +18566,12 @@
         <v>194</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E93" s="2" t="s">
@@ -18589,7 +18589,7 @@
       <c r="I93" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J93" s="3" t="s">
+      <c r="J93" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K93" s="2" t="s">
@@ -18601,13 +18601,13 @@
       <c r="M93" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N93" s="3" t="s">
+      <c r="N93" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O93" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P93" s="3" t="s">
+      <c r="P93" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q93" s="2" t="s">
@@ -18619,7 +18619,7 @@
       <c r="S93" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T93" s="3" t="s">
+      <c r="T93" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U93" s="2" t="s">
@@ -18628,10 +18628,10 @@
       <c r="V93" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W93" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X93" s="3" t="s">
+      <c r="W93" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X93" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y93" s="2" t="s">
@@ -18646,7 +18646,7 @@
       <c r="AB93" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC93" s="3" t="s">
+      <c r="AC93" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD93" s="2" t="s">
@@ -18687,7 +18687,7 @@
       <c r="J94" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="K94" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L94" s="2" t="s">
@@ -18702,7 +18702,7 @@
       <c r="O94" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P94" s="2" t="s">
+      <c r="P94" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Q94" s="2" t="s">
@@ -18711,7 +18711,7 @@
       <c r="R94" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S94" s="2" t="s">
+      <c r="S94" s="3" t="s">
         <v>74</v>
       </c>
       <c r="T94" s="2" t="s">
@@ -18756,7 +18756,7 @@
         <v>196</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>18</v>
@@ -18791,25 +18791,25 @@
       <c r="M95" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N95" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="O95" s="3" t="s">
+      <c r="N95" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O95" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P95" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q95" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="R95" s="2" t="s">
+      <c r="Q95" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R95" s="3" t="s">
         <v>74</v>
       </c>
       <c r="S95" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T95" s="3" t="s">
+      <c r="T95" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U95" s="2" t="s">
@@ -18824,7 +18824,7 @@
       <c r="X95" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y95" s="3" t="s">
+      <c r="Y95" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z95" s="2" t="s">
@@ -18851,12 +18851,12 @@
         <v>197</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E96" s="2" t="s">
@@ -18865,22 +18865,22 @@
       <c r="F96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="G96" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="I96" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K96" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L96" s="3" t="s">
+      <c r="K96" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L96" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M96" s="2" t="s">
@@ -18892,7 +18892,7 @@
       <c r="O96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P96" s="3" t="s">
+      <c r="P96" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q96" s="2" t="s">
@@ -18910,7 +18910,7 @@
       <c r="U96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V96" s="3" t="s">
+      <c r="V96" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W96" s="2" t="s">
@@ -18922,13 +18922,13 @@
       <c r="Y96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z96" s="3" t="s">
+      <c r="Z96" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB96" s="3" t="s">
+      <c r="AB96" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC96" s="2" t="s">
@@ -18937,7 +18937,7 @@
       <c r="AD96" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE96" s="3" t="s">
+      <c r="AE96" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -18951,7 +18951,7 @@
       <c r="C97" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E97" s="2" t="s">
@@ -19002,7 +19002,7 @@
       <c r="T97" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U97" s="3" t="s">
+      <c r="U97" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V97" s="2" t="s">
@@ -19041,7 +19041,7 @@
         <v>199</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>17</v>
@@ -19058,13 +19058,13 @@
       <c r="G98" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H98" s="3" t="s">
+      <c r="H98" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J98" s="3" t="s">
+      <c r="J98" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K98" s="2" t="s">
@@ -19073,7 +19073,7 @@
       <c r="L98" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M98" s="3" t="s">
+      <c r="M98" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N98" s="2" t="s">
@@ -19085,13 +19085,13 @@
       <c r="P98" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q98" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="R98" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="S98" s="3" t="s">
+      <c r="Q98" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R98" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="S98" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T98" s="2" t="s">
@@ -19124,7 +19124,7 @@
       <c r="AC98" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD98" s="3" t="s">
+      <c r="AD98" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE98" s="2" t="s">
@@ -19144,7 +19144,7 @@
       <c r="D99" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="E99" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F99" s="2" t="s">
@@ -19168,10 +19168,10 @@
       <c r="L99" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M99" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="N99" s="2" t="s">
+      <c r="M99" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N99" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O99" s="2" t="s">
@@ -19216,13 +19216,13 @@
       <c r="AB99" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC99" s="3" t="s">
+      <c r="AC99" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD99" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE99" s="3" t="s">
+      <c r="AE99" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -19239,7 +19239,7 @@
       <c r="D100" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E100" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F100" s="2" t="s">
@@ -19260,7 +19260,7 @@
       <c r="K100" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="L100" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M100" s="2" t="s">
@@ -19299,19 +19299,19 @@
       <c r="X100" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y100" s="3" t="s">
+      <c r="Y100" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z100" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA100" s="3" t="s">
+      <c r="AA100" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB100" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC100" s="3" t="s">
+      <c r="AC100" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD100" s="2" t="s">
@@ -19331,19 +19331,19 @@
       <c r="C101" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F101" s="3" t="s">
+      <c r="D101" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="H101" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I101" s="2" t="s">
@@ -19358,10 +19358,10 @@
       <c r="L101" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N101" s="3" t="s">
+      <c r="M101" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N101" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O101" s="2" t="s">
@@ -19370,16 +19370,16 @@
       <c r="P101" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="T101" s="2" t="s">
+      <c r="Q101" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R101" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="S101" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T101" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U101" s="2" t="s">
@@ -19409,7 +19409,7 @@
       <c r="AC101" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD101" s="3" t="s">
+      <c r="AD101" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE101" s="2" t="s">
@@ -19444,7 +19444,7 @@
       <c r="I102" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J102" s="3" t="s">
+      <c r="J102" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K102" s="2" t="s">
@@ -19471,10 +19471,10 @@
       <c r="R102" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S102" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="T102" s="3" t="s">
+      <c r="S102" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="T102" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U102" s="2" t="s">
@@ -19489,7 +19489,7 @@
       <c r="X102" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y102" s="2" t="s">
+      <c r="Y102" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Z102" s="2" t="s">
@@ -19498,7 +19498,7 @@
       <c r="AA102" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB102" s="3" t="s">
+      <c r="AB102" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC102" s="2" t="s">
@@ -19516,7 +19516,7 @@
         <v>204</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>17</v>
@@ -19530,19 +19530,19 @@
       <c r="F103" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G103" s="3" t="s">
+      <c r="G103" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I103" s="3" t="s">
+      <c r="I103" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K103" s="3" t="s">
+      <c r="K103" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L103" s="2" t="s">
@@ -19557,13 +19557,13 @@
       <c r="O103" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="P103" s="3" t="s">
+      <c r="P103" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q103" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R103" s="2" t="s">
+      <c r="R103" s="3" t="s">
         <v>74</v>
       </c>
       <c r="S103" s="2" t="s">
@@ -19578,16 +19578,16 @@
       <c r="V103" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W103" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X103" s="3" t="s">
+      <c r="W103" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X103" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y103" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z103" s="3" t="s">
+      <c r="Z103" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA103" s="2" t="s">
@@ -19676,7 +19676,7 @@
       <c r="W104" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X104" s="3" t="s">
+      <c r="X104" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y104" s="2" t="s">
@@ -19697,7 +19697,7 @@
       <c r="AD104" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE104" s="3" t="s">
+      <c r="AE104" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -19723,7 +19723,7 @@
       <c r="G105" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="H105" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I105" s="2" t="s">
@@ -19765,7 +19765,7 @@
       <c r="U105" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V105" s="3" t="s">
+      <c r="V105" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W105" s="2" t="s">
@@ -19777,16 +19777,16 @@
       <c r="Y105" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z105" s="3" t="s">
+      <c r="Z105" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA105" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB105" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC105" s="3" t="s">
+      <c r="AB105" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC105" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD105" s="2" t="s">
@@ -19806,13 +19806,13 @@
       <c r="C106" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G106" s="2" t="s">
@@ -19896,7 +19896,7 @@
         <v>208</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>18</v>
@@ -19934,7 +19934,7 @@
       <c r="N107" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O107" s="3" t="s">
+      <c r="O107" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P107" s="2" t="s">
@@ -19946,7 +19946,7 @@
       <c r="R107" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S107" s="3" t="s">
+      <c r="S107" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T107" s="2" t="s">
@@ -19964,7 +19964,7 @@
       <c r="X107" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y107" s="3" t="s">
+      <c r="Y107" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z107" s="2" t="s">
@@ -19976,10 +19976,10 @@
       <c r="AB107" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC107" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD107" s="3" t="s">
+      <c r="AC107" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD107" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE107" s="2" t="s">
@@ -19991,7 +19991,7 @@
         <v>209</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>17</v>
@@ -20005,7 +20005,7 @@
       <c r="F108" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="G108" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H108" s="2" t="s">
@@ -20023,22 +20023,22 @@
       <c r="L108" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="M108" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N108" s="3" t="s">
+      <c r="M108" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N108" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O108" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P108" s="2" t="s">
+      <c r="P108" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Q108" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R108" s="3" t="s">
+      <c r="R108" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S108" s="2" t="s">
@@ -20053,7 +20053,7 @@
       <c r="V108" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W108" s="3" t="s">
+      <c r="W108" s="2" t="s">
         <v>74</v>
       </c>
       <c r="X108" s="2" t="s">
@@ -20065,10 +20065,10 @@
       <c r="Z108" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA108" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB108" s="2" t="s">
+      <c r="AA108" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB108" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AC108" s="2" t="s">
@@ -20094,25 +20094,25 @@
       <c r="D109" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E109" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G109" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I109" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J109" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K109" s="3" t="s">
+      <c r="G109" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K109" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L109" s="2" t="s">
@@ -20127,10 +20127,10 @@
       <c r="O109" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P109" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q109" s="3" t="s">
+      <c r="P109" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q109" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R109" s="2" t="s">
@@ -20139,19 +20139,19 @@
       <c r="S109" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T109" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="U109" s="3" t="s">
+      <c r="T109" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="U109" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V109" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W109" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="X109" s="2" t="s">
+      <c r="W109" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X109" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Y109" s="2" t="s">
@@ -20192,7 +20192,7 @@
       <c r="E110" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G110" s="2" t="s">
@@ -20219,7 +20219,7 @@
       <c r="N110" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O110" s="3" t="s">
+      <c r="O110" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P110" s="2" t="s">
@@ -20237,7 +20237,7 @@
       <c r="T110" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U110" s="3" t="s">
+      <c r="U110" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V110" s="2" t="s">
@@ -20246,7 +20246,7 @@
       <c r="W110" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X110" s="3" t="s">
+      <c r="X110" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y110" s="2" t="s">
@@ -20276,7 +20276,7 @@
         <v>212</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>18</v>
@@ -20287,7 +20287,7 @@
       <c r="E111" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="2" t="s">
+      <c r="F111" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G111" s="2" t="s">
@@ -20320,7 +20320,7 @@
       <c r="P111" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q111" s="3" t="s">
+      <c r="Q111" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R111" s="2" t="s">
@@ -20329,7 +20329,7 @@
       <c r="S111" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T111" s="3" t="s">
+      <c r="T111" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U111" s="2" t="s">
@@ -20353,13 +20353,13 @@
       <c r="AA111" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB111" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC111" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD111" s="2" t="s">
+      <c r="AB111" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC111" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD111" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AE111" s="2" t="s">
@@ -20376,7 +20376,7 @@
       <c r="C112" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D112" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E112" s="2" t="s">
@@ -20391,7 +20391,7 @@
       <c r="H112" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I112" s="2" t="s">
+      <c r="I112" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J112" s="2" t="s">
@@ -20442,7 +20442,7 @@
       <c r="Y112" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z112" s="2" t="s">
+      <c r="Z112" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AA112" s="2" t="s">
@@ -20457,7 +20457,7 @@
       <c r="AD112" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE112" s="2" t="s">
+      <c r="AE112" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -20466,12 +20466,12 @@
         <v>214</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E113" s="2" t="s">
@@ -20486,16 +20486,16 @@
       <c r="H113" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I113" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K113" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L113" s="3" t="s">
+      <c r="I113" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L113" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M113" s="2" t="s">
@@ -20510,7 +20510,7 @@
       <c r="P113" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q113" s="2" t="s">
+      <c r="Q113" s="3" t="s">
         <v>74</v>
       </c>
       <c r="R113" s="2" t="s">
@@ -20528,7 +20528,7 @@
       <c r="V113" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W113" s="3" t="s">
+      <c r="W113" s="2" t="s">
         <v>74</v>
       </c>
       <c r="X113" s="2" t="s">
@@ -20549,7 +20549,7 @@
       <c r="AC113" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD113" s="3" t="s">
+      <c r="AD113" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE113" s="2" t="s">
@@ -20561,7 +20561,7 @@
         <v>215</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>17</v>
@@ -20569,13 +20569,13 @@
       <c r="D114" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="E114" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G114" s="3" t="s">
+      <c r="G114" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H114" s="2" t="s">
@@ -20611,7 +20611,7 @@
       <c r="R114" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S114" s="3" t="s">
+      <c r="S114" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T114" s="2" t="s">
@@ -20632,10 +20632,10 @@
       <c r="Y114" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z114" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA114" s="3" t="s">
+      <c r="Z114" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA114" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB114" s="2" t="s">
@@ -20647,7 +20647,7 @@
       <c r="AD114" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE114" s="3" t="s">
+      <c r="AE114" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -20664,7 +20664,7 @@
       <c r="D115" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E115" s="2" t="s">
+      <c r="E115" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F115" s="2" t="s">
@@ -20679,7 +20679,7 @@
       <c r="I115" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J115" s="3" t="s">
+      <c r="J115" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K115" s="2" t="s">
@@ -20688,22 +20688,22 @@
       <c r="L115" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M115" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N115" s="3" t="s">
+      <c r="M115" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N115" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O115" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P115" s="3" t="s">
+      <c r="P115" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q115" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R115" s="2" t="s">
+      <c r="R115" s="3" t="s">
         <v>74</v>
       </c>
       <c r="S115" s="2" t="s">
@@ -20715,7 +20715,7 @@
       <c r="U115" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V115" s="3" t="s">
+      <c r="V115" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W115" s="2" t="s">
@@ -20724,7 +20724,7 @@
       <c r="X115" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y115" s="3" t="s">
+      <c r="Y115" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z115" s="2" t="s">
@@ -20736,7 +20736,7 @@
       <c r="AB115" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC115" s="2" t="s">
+      <c r="AC115" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AD115" s="2" t="s">
@@ -20762,7 +20762,7 @@
       <c r="E116" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F116" s="2" t="s">
+      <c r="F116" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G116" s="2" t="s">
@@ -20798,7 +20798,7 @@
       <c r="Q116" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R116" s="3" t="s">
+      <c r="R116" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S116" s="2" t="s">
@@ -20807,7 +20807,7 @@
       <c r="T116" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U116" s="2" t="s">
+      <c r="U116" s="3" t="s">
         <v>74</v>
       </c>
       <c r="V116" s="2" t="s">
@@ -20822,7 +20822,7 @@
       <c r="Y116" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z116" s="2" t="s">
+      <c r="Z116" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AA116" s="2" t="s">
@@ -20846,7 +20846,7 @@
         <v>218</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>18</v>
@@ -20860,7 +20860,7 @@
       <c r="F117" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="G117" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H117" s="2" t="s">
@@ -20872,16 +20872,16 @@
       <c r="J117" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K117" s="3" t="s">
+      <c r="K117" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L117" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="M117" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="N117" s="3" t="s">
+      <c r="M117" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N117" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O117" s="2" t="s">
@@ -20914,7 +20914,7 @@
       <c r="X117" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y117" s="2" t="s">
+      <c r="Y117" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Z117" s="2" t="s">
@@ -20941,15 +20941,15 @@
         <v>219</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D118" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E118" s="3" t="s">
+      <c r="D118" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F118" s="2" t="s">
@@ -20973,49 +20973,49 @@
       <c r="L118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M118" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N118" s="2" t="s">
+      <c r="M118" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N118" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P118" s="3" t="s">
+      <c r="P118" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R118" s="3" t="s">
+      <c r="R118" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T118" s="3" t="s">
+      <c r="T118" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V118" s="2" t="s">
+      <c r="V118" s="3" t="s">
         <v>74</v>
       </c>
       <c r="W118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X118" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y118" s="3" t="s">
+      <c r="X118" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y118" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA118" s="3" t="s">
+      <c r="AA118" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB118" s="2" t="s">
@@ -21024,7 +21024,7 @@
       <c r="AC118" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD118" s="2" t="s">
+      <c r="AD118" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AE118" s="2" t="s">
@@ -21036,12 +21036,12 @@
         <v>220</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D119" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E119" s="2" t="s">
@@ -21110,7 +21110,7 @@
       <c r="Z119" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA119" s="2" t="s">
+      <c r="AA119" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AB119" s="2" t="s">
@@ -21119,7 +21119,7 @@
       <c r="AC119" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD119" s="3" t="s">
+      <c r="AD119" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE119" s="2" t="s">
@@ -21131,7 +21131,7 @@
         <v>221</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>18</v>
@@ -21142,7 +21142,7 @@
       <c r="E120" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G120" s="2" t="s">
@@ -21169,7 +21169,7 @@
       <c r="N120" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O120" s="2" t="s">
+      <c r="O120" s="3" t="s">
         <v>74</v>
       </c>
       <c r="P120" s="2" t="s">
@@ -21181,7 +21181,7 @@
       <c r="R120" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S120" s="2" t="s">
+      <c r="S120" s="3" t="s">
         <v>74</v>
       </c>
       <c r="T120" s="2" t="s">
@@ -21193,7 +21193,7 @@
       <c r="V120" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W120" s="2" t="s">
+      <c r="W120" s="3" t="s">
         <v>74</v>
       </c>
       <c r="X120" s="2" t="s">
@@ -21211,7 +21211,7 @@
       <c r="AB120" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC120" s="3" t="s">
+      <c r="AC120" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD120" s="2" t="s">
@@ -21246,10 +21246,10 @@
       <c r="H121" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I121" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J121" s="3" t="s">
+      <c r="I121" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J121" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K121" s="2" t="s">
@@ -21264,7 +21264,7 @@
       <c r="N121" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O121" s="3" t="s">
+      <c r="O121" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P121" s="2" t="s">
@@ -21321,7 +21321,7 @@
         <v>223</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>18</v>
@@ -21335,7 +21335,7 @@
       <c r="F122" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G122" s="2" t="s">
+      <c r="G122" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H122" s="2" t="s">
@@ -21347,7 +21347,7 @@
       <c r="J122" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K122" s="2" t="s">
+      <c r="K122" s="3" t="s">
         <v>74</v>
       </c>
       <c r="L122" s="2" t="s">
@@ -21374,7 +21374,7 @@
       <c r="S122" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T122" s="2" t="s">
+      <c r="T122" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U122" s="2" t="s">
@@ -21383,22 +21383,22 @@
       <c r="V122" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W122" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X122" s="2" t="s">
+      <c r="W122" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X122" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Y122" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z122" s="3" t="s">
+      <c r="Z122" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA122" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB122" s="3" t="s">
+      <c r="AB122" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC122" s="2" t="s">
@@ -21407,7 +21407,7 @@
       <c r="AD122" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE122" s="3" t="s">
+      <c r="AE122" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -21416,7 +21416,7 @@
         <v>224</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>17</v>
@@ -21472,10 +21472,10 @@
       <c r="T123" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U123" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="V123" s="3" t="s">
+      <c r="U123" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="V123" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W123" s="2" t="s">
@@ -21528,7 +21528,7 @@
       <c r="G124" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H124" s="3" t="s">
+      <c r="H124" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I124" s="2" t="s">
@@ -21552,7 +21552,7 @@
       <c r="O124" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P124" s="3" t="s">
+      <c r="P124" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q124" s="2" t="s">
@@ -21561,7 +21561,7 @@
       <c r="R124" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S124" s="3" t="s">
+      <c r="S124" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T124" s="2" t="s">
@@ -21588,7 +21588,7 @@
       <c r="AA124" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB124" s="2" t="s">
+      <c r="AB124" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AC124" s="2" t="s">
@@ -21606,7 +21606,7 @@
         <v>226</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>18</v>
@@ -21614,19 +21614,19 @@
       <c r="D125" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E125" s="3" t="s">
+      <c r="E125" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G125" s="3" t="s">
+      <c r="G125" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I125" s="3" t="s">
+      <c r="I125" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J125" s="2" t="s">
@@ -21641,7 +21641,7 @@
       <c r="M125" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N125" s="3" t="s">
+      <c r="N125" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O125" s="2" t="s">
@@ -21662,7 +21662,7 @@
       <c r="T125" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U125" s="3" t="s">
+      <c r="U125" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V125" s="2" t="s">
@@ -21680,7 +21680,7 @@
       <c r="Z125" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA125" s="3" t="s">
+      <c r="AA125" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB125" s="2" t="s">
@@ -21692,7 +21692,7 @@
       <c r="AD125" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE125" s="2" t="s">
+      <c r="AE125" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -21721,10 +21721,10 @@
       <c r="H126" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I126" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J126" s="2" t="s">
+      <c r="I126" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J126" s="3" t="s">
         <v>74</v>
       </c>
       <c r="K126" s="2" t="s">
@@ -21742,7 +21742,7 @@
       <c r="O126" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P126" s="2" t="s">
+      <c r="P126" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Q126" s="2" t="s">
@@ -21754,7 +21754,7 @@
       <c r="S126" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T126" s="3" t="s">
+      <c r="T126" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U126" s="2" t="s">
@@ -21766,7 +21766,7 @@
       <c r="W126" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X126" s="3" t="s">
+      <c r="X126" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y126" s="2" t="s">
@@ -21796,12 +21796,12 @@
         <v>228</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="D127" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E127" s="2" t="s">
@@ -21813,7 +21813,7 @@
       <c r="G127" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H127" s="2" t="s">
+      <c r="H127" s="3" t="s">
         <v>74</v>
       </c>
       <c r="I127" s="2" t="s">
@@ -21834,7 +21834,7 @@
       <c r="N127" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O127" s="3" t="s">
+      <c r="O127" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P127" s="2" t="s">
@@ -21855,7 +21855,7 @@
       <c r="U127" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V127" s="3" t="s">
+      <c r="V127" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W127" s="2" t="s">
@@ -21864,7 +21864,7 @@
       <c r="X127" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y127" s="3" t="s">
+      <c r="Y127" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z127" s="2" t="s">
@@ -21879,7 +21879,7 @@
       <c r="AC127" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD127" s="3" t="s">
+      <c r="AD127" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE127" s="2" t="s">
@@ -21911,19 +21911,19 @@
       <c r="H128" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I128" s="2" t="s">
+      <c r="I128" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K128" s="3" t="s">
+      <c r="K128" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L128" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M128" s="3" t="s">
+      <c r="M128" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N128" s="2" t="s">
@@ -21935,7 +21935,7 @@
       <c r="P128" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q128" s="3" t="s">
+      <c r="Q128" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R128" s="2" t="s">
@@ -21971,13 +21971,13 @@
       <c r="AB128" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC128" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD128" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE128" s="3" t="s">
+      <c r="AC128" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD128" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE128" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -21991,13 +21991,13 @@
       <c r="C129" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="D129" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F129" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G129" s="2" t="s">
@@ -22009,19 +22009,19 @@
       <c r="I129" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J129" s="3" t="s">
+      <c r="J129" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L129" s="3" t="s">
+      <c r="L129" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M129" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N129" s="2" t="s">
+      <c r="N129" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O129" s="2" t="s">
@@ -22057,7 +22057,7 @@
       <c r="Y129" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z129" s="2" t="s">
+      <c r="Z129" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AA129" s="2" t="s">
@@ -22072,7 +22072,7 @@
       <c r="AD129" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE129" s="2" t="s">
+      <c r="AE129" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -22125,7 +22125,7 @@
       <c r="P130" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q130" s="2" t="s">
+      <c r="Q130" s="3" t="s">
         <v>74</v>
       </c>
       <c r="R130" s="2" t="s">
@@ -22152,7 +22152,7 @@
       <c r="Y130" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z130" s="3" t="s">
+      <c r="Z130" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA130" s="2" t="s">
@@ -22161,7 +22161,7 @@
       <c r="AB130" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC130" s="3" t="s">
+      <c r="AC130" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD130" s="2" t="s">
@@ -22232,7 +22232,7 @@
       <c r="T131" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U131" s="2" t="s">
+      <c r="U131" s="3" t="s">
         <v>74</v>
       </c>
       <c r="V131" s="2" t="s">
@@ -22253,7 +22253,7 @@
       <c r="AA131" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB131" s="3" t="s">
+      <c r="AB131" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC131" s="2" t="s">
@@ -22282,13 +22282,13 @@
       <c r="E132" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F132" s="3" t="s">
+      <c r="F132" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H132" s="3" t="s">
+      <c r="H132" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I132" s="2" t="s">
@@ -22306,13 +22306,13 @@
       <c r="M132" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N132" s="3" t="s">
+      <c r="N132" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O132" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P132" s="3" t="s">
+      <c r="P132" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q132" s="2" t="s">
@@ -22333,10 +22333,10 @@
       <c r="V132" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W132" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="X132" s="2" t="s">
+      <c r="W132" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X132" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Y132" s="2" t="s">
@@ -22374,7 +22374,7 @@
       <c r="D133" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E133" s="2" t="s">
+      <c r="E133" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F133" s="2" t="s">
@@ -22389,13 +22389,13 @@
       <c r="I133" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J133" s="3" t="s">
+      <c r="J133" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L133" s="3" t="s">
+      <c r="L133" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M133" s="2" t="s">
@@ -22404,7 +22404,7 @@
       <c r="N133" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O133" s="2" t="s">
+      <c r="O133" s="3" t="s">
         <v>74</v>
       </c>
       <c r="P133" s="2" t="s">
@@ -22437,7 +22437,7 @@
       <c r="Y133" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z133" s="3" t="s">
+      <c r="Z133" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AA133" s="2" t="s">
@@ -22449,7 +22449,7 @@
       <c r="AC133" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD133" s="3" t="s">
+      <c r="AD133" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE133" s="2" t="s">
@@ -22487,7 +22487,7 @@
       <c r="J134" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K134" s="2" t="s">
+      <c r="K134" s="3" t="s">
         <v>74</v>
       </c>
       <c r="L134" s="2" t="s">
@@ -22520,7 +22520,7 @@
       <c r="U134" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V134" s="3" t="s">
+      <c r="V134" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W134" s="2" t="s">
@@ -22541,7 +22541,7 @@
       <c r="AB134" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC134" s="3" t="s">
+      <c r="AC134" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AD134" s="2" t="s">
@@ -22579,7 +22579,7 @@
       <c r="I135" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J135" s="2" t="s">
+      <c r="J135" s="3" t="s">
         <v>74</v>
       </c>
       <c r="K135" s="2" t="s">
@@ -22612,7 +22612,7 @@
       <c r="T135" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="U135" s="3" t="s">
+      <c r="U135" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V135" s="2" t="s">
@@ -22621,7 +22621,7 @@
       <c r="W135" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X135" s="3" t="s">
+      <c r="X135" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y135" s="2" t="s">
@@ -22651,7 +22651,7 @@
         <v>237</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>18</v>
@@ -22662,7 +22662,7 @@
       <c r="E136" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F136" s="2" t="s">
+      <c r="F136" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G136" s="2" t="s">
@@ -22683,7 +22683,7 @@
       <c r="L136" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M136" s="2" t="s">
+      <c r="M136" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N136" s="2" t="s">
@@ -22701,7 +22701,7 @@
       <c r="R136" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S136" s="3" t="s">
+      <c r="S136" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T136" s="2" t="s">
@@ -22719,7 +22719,7 @@
       <c r="X136" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y136" s="3" t="s">
+      <c r="Y136" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z136" s="2" t="s">
@@ -22754,7 +22754,7 @@
       <c r="D137" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E137" s="3" t="s">
+      <c r="E137" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F137" s="2" t="s">
@@ -22772,7 +22772,7 @@
       <c r="J137" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K137" s="3" t="s">
+      <c r="K137" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L137" s="2" t="s">
@@ -22841,7 +22841,7 @@
         <v>239</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>17</v>
@@ -22861,7 +22861,7 @@
       <c r="H138" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I138" s="3" t="s">
+      <c r="I138" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J138" s="2" t="s">
@@ -22870,7 +22870,7 @@
       <c r="K138" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L138" s="2" t="s">
+      <c r="L138" s="3" t="s">
         <v>74</v>
       </c>
       <c r="M138" s="2" t="s">
@@ -22894,7 +22894,7 @@
       <c r="S138" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T138" s="2" t="s">
+      <c r="T138" s="3" t="s">
         <v>74</v>
       </c>
       <c r="U138" s="2" t="s">
@@ -22915,7 +22915,7 @@
       <c r="Z138" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA138" s="3" t="s">
+      <c r="AA138" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB138" s="2" t="s">
@@ -22936,7 +22936,7 @@
         <v>240</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>17</v>
@@ -22989,13 +22989,13 @@
       <c r="S139" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T139" s="3" t="s">
+      <c r="T139" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U139" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V139" s="2" t="s">
+      <c r="V139" s="3" t="s">
         <v>74</v>
       </c>
       <c r="W139" s="2" t="s">
@@ -23031,12 +23031,12 @@
         <v>241</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D140" s="3" t="s">
+      <c r="D140" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E140" s="2" t="s">
@@ -23069,13 +23069,13 @@
       <c r="N140" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O140" s="3" t="s">
+      <c r="O140" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P140" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q140" s="3" t="s">
+      <c r="Q140" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R140" s="2" t="s">
@@ -23117,7 +23117,7 @@
       <c r="AD140" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AE140" s="3" t="s">
+      <c r="AE140" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -23126,7 +23126,7 @@
         <v>242</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>18</v>
@@ -23167,7 +23167,7 @@
       <c r="O141" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P141" s="2" t="s">
+      <c r="P141" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Q141" s="2" t="s">
@@ -23253,7 +23253,7 @@
       <c r="L142" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M142" s="3" t="s">
+      <c r="M142" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N142" s="2" t="s">
@@ -23298,7 +23298,7 @@
       <c r="AA142" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB142" s="3" t="s">
+      <c r="AB142" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AC142" s="2" t="s">
@@ -23321,7 +23321,7 @@
       <c r="C143" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="D143" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E143" s="2" t="s">
@@ -23339,7 +23339,7 @@
       <c r="I143" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J143" s="3" t="s">
+      <c r="J143" s="2" t="s">
         <v>74</v>
       </c>
       <c r="K143" s="2" t="s">
@@ -23351,7 +23351,7 @@
       <c r="M143" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N143" s="3" t="s">
+      <c r="N143" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O143" s="2" t="s">
@@ -23378,13 +23378,13 @@
       <c r="V143" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W143" s="3" t="s">
+      <c r="W143" s="2" t="s">
         <v>74</v>
       </c>
       <c r="X143" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y143" s="2" t="s">
+      <c r="Y143" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Z143" s="2" t="s">
@@ -23393,7 +23393,7 @@
       <c r="AA143" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB143" s="2" t="s">
+      <c r="AB143" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AC143" s="2" t="s">
@@ -23419,13 +23419,13 @@
       <c r="D144" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E144" s="3" t="s">
+      <c r="E144" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G144" s="3" t="s">
+      <c r="G144" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H144" s="2" t="s">
@@ -23437,7 +23437,7 @@
       <c r="J144" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K144" s="3" t="s">
+      <c r="K144" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L144" s="2" t="s">
@@ -23470,22 +23470,22 @@
       <c r="U144" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V144" s="3" t="s">
+      <c r="V144" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W144" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="X144" s="3" t="s">
+      <c r="X144" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Y144" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z144" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA144" s="2" t="s">
+      <c r="Z144" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA144" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AB144" s="2" t="s">
@@ -23556,7 +23556,7 @@
       <c r="R145" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S145" s="2" t="s">
+      <c r="S145" s="3" t="s">
         <v>74</v>
       </c>
       <c r="T145" s="2" t="s">
@@ -23568,19 +23568,19 @@
       <c r="V145" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="W145" s="2" t="s">
+      <c r="W145" s="3" t="s">
         <v>74</v>
       </c>
       <c r="X145" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y145" s="3" t="s">
+      <c r="Y145" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Z145" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA145" s="3" t="s">
+      <c r="AA145" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AB145" s="2" t="s">
@@ -23642,7 +23642,7 @@
       <c r="O146" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P146" s="3" t="s">
+      <c r="P146" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q146" s="2" t="s">
@@ -23654,10 +23654,10 @@
       <c r="S146" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T146" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="U146" s="3" t="s">
+      <c r="T146" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="U146" s="2" t="s">
         <v>74</v>
       </c>
       <c r="V146" s="2" t="s">
@@ -23696,7 +23696,7 @@
         <v>248</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>18</v>
@@ -23707,7 +23707,7 @@
       <c r="E147" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F147" s="2" t="s">
+      <c r="F147" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G147" s="2" t="s">
@@ -23716,7 +23716,7 @@
       <c r="H147" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I147" s="3" t="s">
+      <c r="I147" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J147" s="2" t="s">
@@ -23779,10 +23779,10 @@
       <c r="AC147" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD147" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE147" s="3" t="s">
+      <c r="AD147" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE147" s="2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -23791,7 +23791,7 @@
         <v>249</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>17</v>
@@ -23826,7 +23826,7 @@
       <c r="M148" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="N148" s="2" t="s">
+      <c r="N148" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O148" s="2" t="s">
@@ -23915,7 +23915,7 @@
       <c r="K149" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L149" s="3" t="s">
+      <c r="L149" s="2" t="s">
         <v>74</v>
       </c>
       <c r="M149" s="2" t="s">
@@ -23930,7 +23930,7 @@
       <c r="P149" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q149" s="3" t="s">
+      <c r="Q149" s="2" t="s">
         <v>74</v>
       </c>
       <c r="R149" s="2" t="s">
@@ -23957,7 +23957,7 @@
       <c r="Y149" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Z149" s="2" t="s">
+      <c r="Z149" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AA149" s="2" t="s">
@@ -23966,10 +23966,10 @@
       <c r="AB149" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC149" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD149" s="3" t="s">
+      <c r="AC149" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD149" s="2" t="s">
         <v>74</v>
       </c>
       <c r="AE149" s="2" t="s">
@@ -23981,7 +23981,7 @@
         <v>251</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>18</v>
@@ -23989,7 +23989,7 @@
       <c r="D150" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E150" s="2" t="s">
+      <c r="E150" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F150" s="2" t="s">
@@ -23998,7 +23998,7 @@
       <c r="G150" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H150" s="3" t="s">
+      <c r="H150" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I150" s="2" t="s">
@@ -24013,7 +24013,7 @@
       <c r="L150" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M150" s="2" t="s">
+      <c r="M150" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N150" s="2" t="s">
@@ -24031,7 +24031,7 @@
       <c r="R150" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S150" s="3" t="s">
+      <c r="S150" s="2" t="s">
         <v>74</v>
       </c>
       <c r="T150" s="2" t="s">
@@ -24087,7 +24087,7 @@
       <c r="E151" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F151" s="3" t="s">
+      <c r="F151" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G151" s="2" t="s">
@@ -24108,13 +24108,13 @@
       <c r="L151" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M151" s="3" t="s">
+      <c r="M151" s="2" t="s">
         <v>74</v>
       </c>
       <c r="N151" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="O151" s="3" t="s">
+      <c r="O151" s="2" t="s">
         <v>74</v>
       </c>
       <c r="P151" s="2" t="s">
@@ -24123,13 +24123,13 @@
       <c r="Q151" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="R151" s="3" t="s">
+      <c r="R151" s="2" t="s">
         <v>74</v>
       </c>
       <c r="S151" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T151" s="3" t="s">
+      <c r="T151" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U151" s="2" t="s">
@@ -24153,10 +24153,10 @@
       <c r="AA151" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AB151" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC151" s="2" t="s">
+      <c r="AB151" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC151" s="3" t="s">
         <v>74</v>
       </c>
       <c r="AD151" s="2" t="s">
@@ -24171,7 +24171,7 @@
         <v>253</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>18</v>
@@ -24224,13 +24224,13 @@
       <c r="S152" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T152" s="3" t="s">
+      <c r="T152" s="2" t="s">
         <v>74</v>
       </c>
       <c r="U152" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="V152" s="3" t="s">
+      <c r="V152" s="2" t="s">
         <v>74</v>
       </c>
       <c r="W152" s="2" t="s">
@@ -24239,7 +24239,7 @@
       <c r="X152" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y152" s="2" t="s">
+      <c r="Y152" s="3" t="s">
         <v>74</v>
       </c>
       <c r="Z152" s="2" t="s">
@@ -42521,7 +42521,7 @@
         <v>116</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -42529,7 +42529,7 @@
         <v>117</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -42577,7 +42577,7 @@
         <v>123</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -42593,7 +42593,7 @@
         <v>125</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -42609,7 +42609,7 @@
         <v>127</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -42625,7 +42625,7 @@
         <v>129</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -42665,7 +42665,7 @@
         <v>134</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -42681,7 +42681,7 @@
         <v>136</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
@@ -42697,7 +42697,7 @@
         <v>138</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
@@ -42721,7 +42721,7 @@
         <v>141</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -42737,7 +42737,7 @@
         <v>143</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
@@ -42769,7 +42769,7 @@
         <v>147</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
@@ -42777,7 +42777,7 @@
         <v>148</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -42785,7 +42785,7 @@
         <v>149</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49">
@@ -42793,7 +42793,7 @@
         <v>150</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
@@ -42801,7 +42801,7 @@
         <v>151</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -42809,7 +42809,7 @@
         <v>152</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
@@ -42825,7 +42825,7 @@
         <v>154</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54">
@@ -42833,7 +42833,7 @@
         <v>155</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -42841,7 +42841,7 @@
         <v>156</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -42857,7 +42857,7 @@
         <v>158</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
@@ -42865,7 +42865,7 @@
         <v>159</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
@@ -42873,7 +42873,7 @@
         <v>160</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
@@ -42881,7 +42881,7 @@
         <v>161</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61">
@@ -42913,7 +42913,7 @@
         <v>165</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -42921,7 +42921,7 @@
         <v>166</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66">
@@ -42937,7 +42937,7 @@
         <v>168</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68">
@@ -42945,7 +42945,7 @@
         <v>169</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
@@ -42953,7 +42953,7 @@
         <v>170</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -42977,7 +42977,7 @@
         <v>173</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
@@ -42993,7 +42993,7 @@
         <v>175</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75">
@@ -43001,7 +43001,7 @@
         <v>176</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
@@ -43017,7 +43017,7 @@
         <v>178</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
@@ -43033,7 +43033,7 @@
         <v>180</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -43041,7 +43041,7 @@
         <v>181</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -43049,7 +43049,7 @@
         <v>182</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
@@ -43073,7 +43073,7 @@
         <v>185</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
@@ -43081,7 +43081,7 @@
         <v>186</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
@@ -43097,7 +43097,7 @@
         <v>188</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
@@ -43113,7 +43113,7 @@
         <v>190</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90">
@@ -43129,7 +43129,7 @@
         <v>192</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92">
@@ -43137,7 +43137,7 @@
         <v>193</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93">
@@ -43145,7 +43145,7 @@
         <v>194</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94">
@@ -43161,7 +43161,7 @@
         <v>196</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96">
@@ -43169,7 +43169,7 @@
         <v>197</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97">
@@ -43185,7 +43185,7 @@
         <v>199</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
@@ -43225,7 +43225,7 @@
         <v>204</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
@@ -43257,7 +43257,7 @@
         <v>208</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108">
@@ -43265,7 +43265,7 @@
         <v>209</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109">
@@ -43289,7 +43289,7 @@
         <v>212</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112">
@@ -43305,7 +43305,7 @@
         <v>214</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114">
@@ -43313,7 +43313,7 @@
         <v>215</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115">
@@ -43337,7 +43337,7 @@
         <v>218</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118">
@@ -43345,7 +43345,7 @@
         <v>219</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119">
@@ -43353,7 +43353,7 @@
         <v>220</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120">
@@ -43361,7 +43361,7 @@
         <v>221</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121">
@@ -43377,7 +43377,7 @@
         <v>223</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123">
@@ -43385,7 +43385,7 @@
         <v>224</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124">
@@ -43401,7 +43401,7 @@
         <v>226</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126">
@@ -43417,7 +43417,7 @@
         <v>228</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128">
@@ -43489,7 +43489,7 @@
         <v>237</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="137">
@@ -43505,7 +43505,7 @@
         <v>239</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139">
@@ -43513,7 +43513,7 @@
         <v>240</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="140">
@@ -43521,7 +43521,7 @@
         <v>241</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="141">
@@ -43529,7 +43529,7 @@
         <v>242</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142">
@@ -43577,7 +43577,7 @@
         <v>248</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="148">
@@ -43585,7 +43585,7 @@
         <v>249</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="149">
@@ -43601,7 +43601,7 @@
         <v>251</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151">
@@ -43617,7 +43617,7 @@
         <v>253</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
